--- a/feedback_forms/010_skin_tone_finder_quiz--feedback_forms.xlsx
+++ b/feedback_forms/010_skin_tone_finder_quiz--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -848,29 +848,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cool</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cool</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_undertone_choices</t>
+          <t>skin_tone_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>porcelain</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Porcelain</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>porcelain</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Porcelain</t>
+          <t>Olive</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>golden</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>Golden</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>golden</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -967,29 +967,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Dark</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>skin_tone_choices</t>
+          <t>select_beauty_type_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>porcelain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Porcelain</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>porcelain</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Porcelain</t>
+          <t>Olive</t>
         </is>
       </c>
     </row>
@@ -1035,29 +1035,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>golden</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>Golden</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_beauty_type_choices</t>
+          <t>select_accurate_recommendation_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>golden</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>porcelain</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Porcelain</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>porcelain</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Porcelain</t>
+          <t>Olive</t>
         </is>
       </c>
     </row>
@@ -1103,29 +1103,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>golden</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>Golden</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_accurate_recommendation_choices</t>
+          <t>select_product_type_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>golden</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>porcelain</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Porcelain</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>porcelain</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Porcelain</t>
+          <t>Olive</t>
         </is>
       </c>
     </row>
@@ -1171,29 +1171,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>golden</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>Golden</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_product_type_choices</t>
+          <t>select_quiz_completed_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>golden</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1205,27 +1205,10 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_quiz_completed_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
